--- a/Herbivory25v1.xlsx
+++ b/Herbivory25v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A80FC666-903C-4590-9B69-CD1A63248A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAE0A73-049A-4089-8293-127E88AC7899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3DE77797-FE37-4DE0-A864-CE2A3E67F667}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>Treatment</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>C-MBB-8</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>C-Pf-4</t>
@@ -634,31 +631,28 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="E5">
-        <v>16.5</v>
+        <v>23.5</v>
       </c>
       <c r="F5">
-        <v>23.5</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>14</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="I5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J5">
-        <v>11.5</v>
-      </c>
-      <c r="K5">
         <v>11.5</v>
       </c>
     </row>
@@ -667,7 +661,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -702,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -737,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>11</v>
@@ -772,318 +766,291 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>21.5</v>
       </c>
       <c r="E9">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="F9">
-        <v>22.5</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H9">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="I9">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>7.5</v>
       </c>
-      <c r="K9">
-        <v>7.5</v>
-      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>24.5</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10">
-        <v>19</v>
-      </c>
-      <c r="F10">
-        <v>24.5</v>
-      </c>
-      <c r="G10">
-        <v>16</v>
-      </c>
       <c r="H10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>9</v>
-      </c>
-      <c r="K10">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
       <c r="D11">
-        <v>12</v>
+        <v>21.5</v>
       </c>
       <c r="E11">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="F11">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="G11">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="H11">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>9</v>
       </c>
       <c r="J11">
-        <v>9</v>
-      </c>
-      <c r="K11">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
       <c r="D12">
-        <v>12</v>
+        <v>21.5</v>
       </c>
       <c r="E12">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="F12">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="G12">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="H12">
         <v>10.5</v>
       </c>
       <c r="I12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>10</v>
-      </c>
-      <c r="K12">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>22.5</v>
       </c>
       <c r="E13">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="F13">
-        <v>28.5</v>
+        <v>16.5</v>
       </c>
       <c r="G13">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="H13">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="I13">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>9</v>
-      </c>
-      <c r="K13">
         <v>8.5</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
       <c r="D14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>33.5</v>
       </c>
       <c r="F14">
-        <v>33.5</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="H14">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>8</v>
       </c>
-      <c r="K14">
-        <v>8</v>
-      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>11.5</v>
       </c>
       <c r="D15">
+        <v>19.5</v>
+      </c>
+      <c r="E15">
+        <v>25.5</v>
+      </c>
+      <c r="F15">
+        <v>16.5</v>
+      </c>
+      <c r="G15">
         <v>11.5</v>
-      </c>
-      <c r="E15">
-        <v>19.5</v>
-      </c>
-      <c r="F15">
-        <v>25.5</v>
-      </c>
-      <c r="G15">
-        <v>16.5</v>
       </c>
       <c r="H15">
         <v>11.5</v>
       </c>
       <c r="I15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J15">
-        <v>11</v>
-      </c>
-      <c r="K15">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>19.5</v>
+      </c>
+      <c r="E16">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>26</v>
+      </c>
+      <c r="G16">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="H16">
+        <v>11.5</v>
+      </c>
+      <c r="I16">
+        <v>9</v>
+      </c>
+      <c r="J16">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17">
         <v>7</v>
       </c>
-      <c r="D16">
-        <v>11</v>
-      </c>
-      <c r="E16">
-        <v>19.5</v>
-      </c>
-      <c r="F16">
+      <c r="D17">
+        <v>19</v>
+      </c>
+      <c r="E17">
         <v>28</v>
       </c>
-      <c r="G16">
-        <v>26</v>
-      </c>
-      <c r="H16">
-        <v>12</v>
-      </c>
-      <c r="I16">
-        <v>11.5</v>
-      </c>
-      <c r="J16">
-        <v>9</v>
-      </c>
-      <c r="K16">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>19</v>
-      </c>
       <c r="F17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G17">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="H17">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="I17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>10</v>
-      </c>
-      <c r="K17">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:K5">
+  <conditionalFormatting sqref="C5:J5">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
